--- a/data/DevSec_study_plan.xlsx
+++ b/data/DevSec_study_plan.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/justin/Desktop/Justin/cisco_sandboxes/Dev_sec_plan/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/justin/Desktop/Justin/PycharmProjects/ansible_dev/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8314B12D-B864-7D42-ABAE-B1D8E17CC918}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{413A58CF-F02F-654C-840E-2EB6C477E35C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="880" windowWidth="36000" windowHeight="21540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ACI_CONTRACTS" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="63">
   <si>
     <t>CONSUMED_EPG</t>
   </si>
@@ -154,12 +154,6 @@
     <t>SUBJ_VZANY-to-EPG_DC</t>
   </si>
   <si>
-    <t>DNS_FLT</t>
-  </si>
-  <si>
-    <t>DNS</t>
-  </si>
-  <si>
     <t>N</t>
   </si>
   <si>
@@ -169,48 +163,6 @@
     <t>Port for Domain Controller Services</t>
   </si>
   <si>
-    <t>DNS_TCP_FLT</t>
-  </si>
-  <si>
-    <t>DNS_UDP_FLT</t>
-  </si>
-  <si>
-    <t>udp</t>
-  </si>
-  <si>
-    <t>GLOBAL_CATALOG_FLT</t>
-  </si>
-  <si>
-    <t>GLOBAL_CATALOG2_FLT</t>
-  </si>
-  <si>
-    <t>KERBEROS_FLT</t>
-  </si>
-  <si>
-    <t>KERBEROS_PASS_TCP_FLT</t>
-  </si>
-  <si>
-    <t>KERBEROS_PASS_UDP_FLT</t>
-  </si>
-  <si>
-    <t>LDAP_SSL_FLT</t>
-  </si>
-  <si>
-    <t>NTP_UDP_FLT</t>
-  </si>
-  <si>
-    <t>RPC_ENDPOINT_MAPPER_FLT</t>
-  </si>
-  <si>
-    <t>RPC_EPHERMERAL_FLT</t>
-  </si>
-  <si>
-    <t>LDAP_TCP_FLT</t>
-  </si>
-  <si>
-    <t>LDAP_UDP_FLT</t>
-  </si>
-  <si>
     <t>SMB_FLT</t>
   </si>
   <si>
@@ -236,6 +188,27 @@
   </si>
   <si>
     <t>DaVinci Robots 151.211.171.2 &amp; 151.211.164.8 to RFL-INTUITIVE 151.211.211.129 - Application Updates</t>
+  </si>
+  <si>
+    <t>EPG_DCF</t>
+  </si>
+  <si>
+    <t>CON_VZANY-to-EPG_DCF</t>
+  </si>
+  <si>
+    <t>Any EPG to DCF</t>
+  </si>
+  <si>
+    <t>SUBJ_VZANY-to-EPG_DCF</t>
+  </si>
+  <si>
+    <t>EPG_RFH_CLUBS</t>
+  </si>
+  <si>
+    <t>Justin</t>
+  </si>
+  <si>
+    <t>Created by Ansible</t>
   </si>
 </sst>
 </file>
@@ -254,7 +227,6 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -599,10 +571,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S21"/>
+  <dimension ref="A1:S9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="21.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="44" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="44.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="28.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="23.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="8" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.83203125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="28.5" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="110" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.2">
@@ -666,28 +654,28 @@
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B2" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="D2" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="E2" t="s">
         <v>23</v>
       </c>
       <c r="F2" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="G2" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="I2" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="J2" t="s">
         <v>26</v>
@@ -696,10 +684,10 @@
         <v>27</v>
       </c>
       <c r="L2">
-        <v>2101</v>
+        <v>1434</v>
       </c>
       <c r="M2">
-        <v>2101</v>
+        <v>1434</v>
       </c>
       <c r="N2" t="s">
         <v>28</v>
@@ -714,33 +702,36 @@
         <v>31</v>
       </c>
       <c r="S2" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="B3" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="C3" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="D3" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="E3" t="s">
         <v>23</v>
       </c>
       <c r="F3" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="G3" t="s">
-        <v>37</v>
+        <v>45</v>
+      </c>
+      <c r="H3" t="s">
+        <v>46</v>
       </c>
       <c r="I3" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="J3" t="s">
         <v>26</v>
@@ -749,25 +740,16 @@
         <v>27</v>
       </c>
       <c r="L3">
-        <v>1434</v>
+        <v>445</v>
       </c>
       <c r="M3">
-        <v>1434</v>
+        <v>445</v>
       </c>
       <c r="N3" t="s">
         <v>28</v>
       </c>
-      <c r="O3" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>30</v>
-      </c>
-      <c r="R3" t="s">
-        <v>31</v>
-      </c>
-      <c r="S3" t="s">
-        <v>38</v>
+      <c r="P3" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.2">
@@ -790,13 +772,13 @@
         <v>43</v>
       </c>
       <c r="G4" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="H4" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="I4" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="J4" t="s">
         <v>26</v>
@@ -805,45 +787,42 @@
         <v>27</v>
       </c>
       <c r="L4">
-        <v>53</v>
+        <v>443</v>
       </c>
       <c r="M4">
-        <v>53</v>
+        <v>443</v>
       </c>
       <c r="N4" t="s">
         <v>28</v>
       </c>
       <c r="P4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="C5" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="D5" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="E5" t="s">
         <v>23</v>
       </c>
       <c r="F5" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="G5" t="s">
-        <v>47</v>
-      </c>
-      <c r="H5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="I5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J5" t="s">
         <v>26</v>
@@ -852,63 +831,78 @@
         <v>27</v>
       </c>
       <c r="L5">
-        <v>53</v>
+        <v>135</v>
       </c>
       <c r="M5">
-        <v>53</v>
+        <v>135</v>
       </c>
       <c r="N5" t="s">
         <v>28</v>
       </c>
-      <c r="P5" t="s">
-        <v>46</v>
+      <c r="O5" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>30</v>
+      </c>
+      <c r="R5" t="s">
+        <v>31</v>
+      </c>
+      <c r="S5" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="B6" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="C6" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="D6" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="E6" t="s">
         <v>23</v>
       </c>
       <c r="F6" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="G6" t="s">
-        <v>47</v>
-      </c>
-      <c r="H6" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="I6" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="J6" t="s">
         <v>26</v>
       </c>
       <c r="K6" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="L6">
-        <v>53</v>
+        <v>8888</v>
       </c>
       <c r="M6">
-        <v>53</v>
+        <v>8888</v>
       </c>
       <c r="N6" t="s">
         <v>28</v>
       </c>
-      <c r="P6" t="s">
-        <v>46</v>
+      <c r="O6" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>30</v>
+      </c>
+      <c r="R6" t="s">
+        <v>31</v>
+      </c>
+      <c r="S6" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.2">
@@ -916,28 +910,28 @@
         <v>39</v>
       </c>
       <c r="B7" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="C7" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="D7" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="E7" t="s">
         <v>23</v>
       </c>
       <c r="F7" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="G7" t="s">
+        <v>45</v>
+      </c>
+      <c r="H7" t="s">
+        <v>46</v>
+      </c>
+      <c r="I7" t="s">
         <v>47</v>
-      </c>
-      <c r="H7" t="s">
-        <v>48</v>
-      </c>
-      <c r="I7" t="s">
-        <v>52</v>
       </c>
       <c r="J7" t="s">
         <v>26</v>
@@ -946,45 +940,42 @@
         <v>27</v>
       </c>
       <c r="L7">
-        <v>3268</v>
+        <v>445</v>
       </c>
       <c r="M7">
-        <v>3268</v>
+        <v>445</v>
       </c>
       <c r="N7" t="s">
         <v>28</v>
       </c>
       <c r="P7" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="B8" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="C8" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="D8" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="E8" t="s">
         <v>23</v>
       </c>
       <c r="F8" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="G8" t="s">
-        <v>47</v>
-      </c>
-      <c r="H8" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="I8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J8" t="s">
         <v>26</v>
@@ -993,45 +984,51 @@
         <v>27</v>
       </c>
       <c r="L8">
-        <v>3269</v>
+        <v>8888</v>
       </c>
       <c r="M8">
-        <v>3269</v>
+        <v>8888</v>
       </c>
       <c r="N8" t="s">
         <v>28</v>
       </c>
-      <c r="P8" t="s">
-        <v>46</v>
+      <c r="O8" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>61</v>
+      </c>
+      <c r="R8" t="s">
+        <v>31</v>
+      </c>
+      <c r="S8" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="C9" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="D9" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="E9" t="s">
         <v>23</v>
       </c>
       <c r="F9" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="G9" t="s">
-        <v>47</v>
-      </c>
-      <c r="H9" t="s">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="I9" t="s">
-        <v>54</v>
+        <v>25</v>
       </c>
       <c r="J9" t="s">
         <v>26</v>
@@ -1040,592 +1037,25 @@
         <v>27</v>
       </c>
       <c r="L9">
-        <v>88</v>
+        <v>2101</v>
       </c>
       <c r="M9">
-        <v>88</v>
+        <v>2101</v>
       </c>
       <c r="N9" t="s">
         <v>28</v>
       </c>
-      <c r="P9" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>39</v>
-      </c>
-      <c r="B10" t="s">
-        <v>40</v>
-      </c>
-      <c r="C10" t="s">
-        <v>41</v>
-      </c>
-      <c r="D10" t="s">
-        <v>42</v>
-      </c>
-      <c r="E10" t="s">
-        <v>23</v>
-      </c>
-      <c r="F10" t="s">
-        <v>43</v>
-      </c>
-      <c r="G10" t="s">
-        <v>47</v>
-      </c>
-      <c r="H10" t="s">
-        <v>48</v>
-      </c>
-      <c r="I10" t="s">
-        <v>55</v>
-      </c>
-      <c r="J10" t="s">
-        <v>26</v>
-      </c>
-      <c r="K10" t="s">
-        <v>27</v>
-      </c>
-      <c r="L10">
-        <v>464</v>
-      </c>
-      <c r="M10">
-        <v>88</v>
-      </c>
-      <c r="N10" t="s">
-        <v>28</v>
-      </c>
-      <c r="P10" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>39</v>
-      </c>
-      <c r="B11" t="s">
-        <v>40</v>
-      </c>
-      <c r="C11" t="s">
-        <v>41</v>
-      </c>
-      <c r="D11" t="s">
-        <v>42</v>
-      </c>
-      <c r="E11" t="s">
-        <v>23</v>
-      </c>
-      <c r="F11" t="s">
-        <v>43</v>
-      </c>
-      <c r="G11" t="s">
-        <v>47</v>
-      </c>
-      <c r="H11" t="s">
-        <v>48</v>
-      </c>
-      <c r="I11" t="s">
-        <v>56</v>
-      </c>
-      <c r="J11" t="s">
-        <v>26</v>
-      </c>
-      <c r="K11" t="s">
-        <v>51</v>
-      </c>
-      <c r="L11">
-        <v>464</v>
-      </c>
-      <c r="M11">
-        <v>88</v>
-      </c>
-      <c r="N11" t="s">
-        <v>28</v>
-      </c>
-      <c r="P11" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>39</v>
-      </c>
-      <c r="B12" t="s">
-        <v>40</v>
-      </c>
-      <c r="C12" t="s">
-        <v>41</v>
-      </c>
-      <c r="D12" t="s">
-        <v>42</v>
-      </c>
-      <c r="E12" t="s">
-        <v>23</v>
-      </c>
-      <c r="F12" t="s">
-        <v>43</v>
-      </c>
-      <c r="G12" t="s">
-        <v>47</v>
-      </c>
-      <c r="H12" t="s">
-        <v>48</v>
-      </c>
-      <c r="I12" t="s">
-        <v>57</v>
-      </c>
-      <c r="J12" t="s">
-        <v>26</v>
-      </c>
-      <c r="K12" t="s">
-        <v>27</v>
-      </c>
-      <c r="L12">
-        <v>636</v>
-      </c>
-      <c r="M12">
-        <v>636</v>
-      </c>
-      <c r="N12" t="s">
-        <v>28</v>
-      </c>
-      <c r="P12" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>39</v>
-      </c>
-      <c r="B13" t="s">
-        <v>40</v>
-      </c>
-      <c r="C13" t="s">
-        <v>41</v>
-      </c>
-      <c r="D13" t="s">
-        <v>42</v>
-      </c>
-      <c r="E13" t="s">
-        <v>23</v>
-      </c>
-      <c r="F13" t="s">
-        <v>43</v>
-      </c>
-      <c r="G13" t="s">
-        <v>47</v>
-      </c>
-      <c r="H13" t="s">
-        <v>48</v>
-      </c>
-      <c r="I13" t="s">
-        <v>58</v>
-      </c>
-      <c r="J13" t="s">
-        <v>26</v>
-      </c>
-      <c r="K13" t="s">
-        <v>51</v>
-      </c>
-      <c r="L13">
-        <v>123</v>
-      </c>
-      <c r="M13">
-        <v>123</v>
-      </c>
-      <c r="N13" t="s">
-        <v>28</v>
-      </c>
-      <c r="P13" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>39</v>
-      </c>
-      <c r="B14" t="s">
-        <v>40</v>
-      </c>
-      <c r="C14" t="s">
-        <v>41</v>
-      </c>
-      <c r="D14" t="s">
-        <v>42</v>
-      </c>
-      <c r="E14" t="s">
-        <v>23</v>
-      </c>
-      <c r="F14" t="s">
-        <v>43</v>
-      </c>
-      <c r="G14" t="s">
-        <v>47</v>
-      </c>
-      <c r="H14" t="s">
-        <v>48</v>
-      </c>
-      <c r="I14" t="s">
-        <v>59</v>
-      </c>
-      <c r="J14" t="s">
-        <v>26</v>
-      </c>
-      <c r="K14" t="s">
-        <v>27</v>
-      </c>
-      <c r="L14">
-        <v>135</v>
-      </c>
-      <c r="M14">
-        <v>135</v>
-      </c>
-      <c r="N14" t="s">
-        <v>28</v>
-      </c>
-      <c r="P14" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>39</v>
-      </c>
-      <c r="B15" t="s">
-        <v>40</v>
-      </c>
-      <c r="C15" t="s">
-        <v>41</v>
-      </c>
-      <c r="D15" t="s">
-        <v>42</v>
-      </c>
-      <c r="E15" t="s">
-        <v>23</v>
-      </c>
-      <c r="F15" t="s">
-        <v>43</v>
-      </c>
-      <c r="G15" t="s">
-        <v>47</v>
-      </c>
-      <c r="H15" t="s">
-        <v>48</v>
-      </c>
-      <c r="I15" t="s">
-        <v>60</v>
-      </c>
-      <c r="J15" t="s">
-        <v>26</v>
-      </c>
-      <c r="K15" t="s">
-        <v>27</v>
-      </c>
-      <c r="L15">
-        <v>49152</v>
-      </c>
-      <c r="M15">
-        <v>65535</v>
-      </c>
-      <c r="N15" t="s">
-        <v>28</v>
-      </c>
-      <c r="P15" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>39</v>
-      </c>
-      <c r="B16" t="s">
-        <v>40</v>
-      </c>
-      <c r="C16" t="s">
-        <v>41</v>
-      </c>
-      <c r="D16" t="s">
-        <v>42</v>
-      </c>
-      <c r="E16" t="s">
-        <v>23</v>
-      </c>
-      <c r="F16" t="s">
-        <v>43</v>
-      </c>
-      <c r="G16" t="s">
-        <v>47</v>
-      </c>
-      <c r="H16" t="s">
-        <v>48</v>
-      </c>
-      <c r="I16" t="s">
-        <v>61</v>
-      </c>
-      <c r="J16" t="s">
-        <v>26</v>
-      </c>
-      <c r="K16" t="s">
-        <v>27</v>
-      </c>
-      <c r="L16">
-        <v>389</v>
-      </c>
-      <c r="M16">
-        <v>389</v>
-      </c>
-      <c r="N16" t="s">
-        <v>28</v>
-      </c>
-      <c r="P16" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>39</v>
-      </c>
-      <c r="B17" t="s">
-        <v>40</v>
-      </c>
-      <c r="C17" t="s">
-        <v>41</v>
-      </c>
-      <c r="D17" t="s">
-        <v>42</v>
-      </c>
-      <c r="E17" t="s">
-        <v>23</v>
-      </c>
-      <c r="F17" t="s">
-        <v>43</v>
-      </c>
-      <c r="G17" t="s">
-        <v>47</v>
-      </c>
-      <c r="H17" t="s">
-        <v>48</v>
-      </c>
-      <c r="I17" t="s">
-        <v>62</v>
-      </c>
-      <c r="J17" t="s">
-        <v>26</v>
-      </c>
-      <c r="K17" t="s">
-        <v>51</v>
-      </c>
-      <c r="L17">
-        <v>389</v>
-      </c>
-      <c r="M17">
-        <v>389</v>
-      </c>
-      <c r="N17" t="s">
-        <v>28</v>
-      </c>
-      <c r="P17" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>39</v>
-      </c>
-      <c r="B18" t="s">
-        <v>40</v>
-      </c>
-      <c r="C18" t="s">
-        <v>41</v>
-      </c>
-      <c r="D18" t="s">
-        <v>42</v>
-      </c>
-      <c r="E18" t="s">
-        <v>23</v>
-      </c>
-      <c r="F18" t="s">
-        <v>43</v>
-      </c>
-      <c r="G18" t="s">
-        <v>47</v>
-      </c>
-      <c r="H18" t="s">
-        <v>48</v>
-      </c>
-      <c r="I18" t="s">
-        <v>63</v>
-      </c>
-      <c r="J18" t="s">
-        <v>26</v>
-      </c>
-      <c r="K18" t="s">
-        <v>27</v>
-      </c>
-      <c r="L18">
-        <v>445</v>
-      </c>
-      <c r="M18">
-        <v>445</v>
-      </c>
-      <c r="N18" t="s">
-        <v>28</v>
-      </c>
-      <c r="P18" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>39</v>
-      </c>
-      <c r="B19" t="s">
-        <v>40</v>
-      </c>
-      <c r="C19" t="s">
-        <v>41</v>
-      </c>
-      <c r="D19" t="s">
-        <v>42</v>
-      </c>
-      <c r="E19" t="s">
-        <v>23</v>
-      </c>
-      <c r="F19" t="s">
-        <v>43</v>
-      </c>
-      <c r="G19" t="s">
-        <v>64</v>
-      </c>
-      <c r="H19" t="s">
-        <v>65</v>
-      </c>
-      <c r="I19" t="s">
-        <v>64</v>
-      </c>
-      <c r="J19" t="s">
-        <v>26</v>
-      </c>
-      <c r="K19" t="s">
-        <v>27</v>
-      </c>
-      <c r="L19">
-        <v>443</v>
-      </c>
-      <c r="M19">
-        <v>443</v>
-      </c>
-      <c r="N19" t="s">
-        <v>28</v>
-      </c>
-      <c r="P19" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>19</v>
-      </c>
-      <c r="B20" t="s">
-        <v>20</v>
-      </c>
-      <c r="C20" t="s">
-        <v>21</v>
-      </c>
-      <c r="D20" t="s">
-        <v>22</v>
-      </c>
-      <c r="E20" t="s">
-        <v>23</v>
-      </c>
-      <c r="F20" t="s">
-        <v>24</v>
-      </c>
-      <c r="G20" t="s">
-        <v>66</v>
-      </c>
-      <c r="I20" t="s">
-        <v>66</v>
-      </c>
-      <c r="J20" t="s">
-        <v>26</v>
-      </c>
-      <c r="K20" t="s">
-        <v>27</v>
-      </c>
-      <c r="L20">
-        <v>135</v>
-      </c>
-      <c r="M20">
-        <v>135</v>
-      </c>
-      <c r="N20" t="s">
-        <v>28</v>
-      </c>
-      <c r="O20" t="s">
+      <c r="O9" t="s">
         <v>29</v>
       </c>
-      <c r="Q20" t="s">
+      <c r="Q9" t="s">
         <v>30</v>
       </c>
-      <c r="R20" t="s">
+      <c r="R9" t="s">
         <v>31</v>
       </c>
-      <c r="S20" t="s">
+      <c r="S9" t="s">
         <v>32</v>
-      </c>
-    </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>67</v>
-      </c>
-      <c r="B21" t="s">
-        <v>20</v>
-      </c>
-      <c r="C21" t="s">
-        <v>68</v>
-      </c>
-      <c r="D21" t="s">
-        <v>22</v>
-      </c>
-      <c r="E21" t="s">
-        <v>23</v>
-      </c>
-      <c r="F21" t="s">
-        <v>69</v>
-      </c>
-      <c r="G21" t="s">
-        <v>70</v>
-      </c>
-      <c r="I21" t="s">
-        <v>70</v>
-      </c>
-      <c r="J21" t="s">
-        <v>26</v>
-      </c>
-      <c r="K21" t="s">
-        <v>27</v>
-      </c>
-      <c r="L21">
-        <v>8888</v>
-      </c>
-      <c r="M21">
-        <v>8888</v>
-      </c>
-      <c r="N21" t="s">
-        <v>28</v>
-      </c>
-      <c r="O21" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q21" t="s">
-        <v>30</v>
-      </c>
-      <c r="R21" t="s">
-        <v>31</v>
-      </c>
-      <c r="S21" t="s">
-        <v>71</v>
       </c>
     </row>
   </sheetData>

--- a/data/DevSec_study_plan.xlsx
+++ b/data/DevSec_study_plan.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/justin/Desktop/Justin/PycharmProjects/ansible_dev/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{413A58CF-F02F-654C-840E-2EB6C477E35C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13FA93CC-EEDF-B04D-976F-4BD453987EF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="880" windowWidth="36000" windowHeight="21540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15040" yWindow="-21100" windowWidth="38400" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ACI_CONTRACTS" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="60">
   <si>
     <t>CONSUMED_EPG</t>
   </si>
@@ -76,9 +76,6 @@
     <t>INCLUDED IN VZANY DEFAULT RULE</t>
   </si>
   <si>
-    <t>NOTES</t>
-  </si>
-  <si>
     <t>EPG_L3OUT</t>
   </si>
   <si>
@@ -118,9 +115,6 @@
     <t>Yes</t>
   </si>
   <si>
-    <t>DaVinci Robots 151.211.171.2 &amp; 151.211.164.8 to RFL-INTUITIVE 151.211.211.129  - MSMQ - Microsoft Message Queue</t>
-  </si>
-  <si>
     <t>EPG_151.211.208.0</t>
   </si>
   <si>
@@ -136,9 +130,6 @@
     <t>TCP_1434_FLT</t>
   </si>
   <si>
-    <t>RFL-INTUITIVE 151.211.211.129 to SQL Database ,SQL Cluster IP - 151.211.208.87, SQL Instance (SQL-CLIN01-02\INST01) IP: 151.211.209.15</t>
-  </si>
-  <si>
     <t>VZANY</t>
   </si>
   <si>
@@ -187,9 +178,6 @@
     <t>TCP_8888_FLT</t>
   </si>
   <si>
-    <t>DaVinci Robots 151.211.171.2 &amp; 151.211.164.8 to RFL-INTUITIVE 151.211.211.129 - Application Updates</t>
-  </si>
-  <si>
     <t>EPG_DCF</t>
   </si>
   <si>
@@ -208,14 +196,17 @@
     <t>Justin</t>
   </si>
   <si>
-    <t>Created by Ansible</t>
+    <t>STATUS</t>
+  </si>
+  <si>
+    <t>Done</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -227,6 +218,12 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -264,9 +261,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -590,7 +590,7 @@
     <col min="16" max="16" width="8" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="10.83203125" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="28.5" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="110" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="6.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.2">
@@ -648,40 +648,40 @@
       <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
-        <v>18</v>
+      <c r="S1" s="2" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D2" t="s">
         <v>33</v>
       </c>
-      <c r="C2" t="s">
+      <c r="E2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2" t="s">
         <v>34</v>
       </c>
-      <c r="D2" t="s">
+      <c r="G2" t="s">
         <v>35</v>
       </c>
-      <c r="E2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F2" t="s">
-        <v>36</v>
-      </c>
-      <c r="G2" t="s">
-        <v>37</v>
-      </c>
       <c r="I2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="J2" t="s">
+        <v>25</v>
+      </c>
+      <c r="K2" t="s">
         <v>26</v>
-      </c>
-      <c r="K2" t="s">
-        <v>27</v>
       </c>
       <c r="L2">
         <v>1434</v>
@@ -690,54 +690,54 @@
         <v>1434</v>
       </c>
       <c r="N2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O2" t="s">
         <v>28</v>
       </c>
-      <c r="O2" t="s">
+      <c r="Q2" t="s">
         <v>29</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="R2" t="s">
         <v>30</v>
       </c>
-      <c r="R2" t="s">
-        <v>31</v>
-      </c>
       <c r="S2" t="s">
-        <v>38</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D3" t="s">
         <v>39</v>
       </c>
-      <c r="B3" t="s">
+      <c r="E3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" t="s">
         <v>40</v>
       </c>
-      <c r="C3" t="s">
-        <v>41</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="G3" t="s">
         <v>42</v>
       </c>
-      <c r="E3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F3" t="s">
+      <c r="H3" t="s">
         <v>43</v>
       </c>
-      <c r="G3" t="s">
-        <v>45</v>
-      </c>
-      <c r="H3" t="s">
-        <v>46</v>
-      </c>
       <c r="I3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="J3" t="s">
+        <v>25</v>
+      </c>
+      <c r="K3" t="s">
         <v>26</v>
-      </c>
-      <c r="K3" t="s">
-        <v>27</v>
       </c>
       <c r="L3">
         <v>445</v>
@@ -746,45 +746,45 @@
         <v>445</v>
       </c>
       <c r="N3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P3" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D4" t="s">
         <v>39</v>
       </c>
-      <c r="B4" t="s">
+      <c r="E4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" t="s">
         <v>40</v>
       </c>
-      <c r="C4" t="s">
-        <v>41</v>
-      </c>
-      <c r="D4" t="s">
-        <v>42</v>
-      </c>
-      <c r="E4" t="s">
-        <v>23</v>
-      </c>
-      <c r="F4" t="s">
-        <v>43</v>
-      </c>
       <c r="G4" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H4" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="I4" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="J4" t="s">
+        <v>25</v>
+      </c>
+      <c r="K4" t="s">
         <v>26</v>
-      </c>
-      <c r="K4" t="s">
-        <v>27</v>
       </c>
       <c r="L4">
         <v>443</v>
@@ -793,42 +793,42 @@
         <v>443</v>
       </c>
       <c r="N4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P4" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" t="s">
         <v>19</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>20</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>21</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>22</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>23</v>
       </c>
-      <c r="F5" t="s">
-        <v>24</v>
-      </c>
       <c r="G5" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="I5" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="J5" t="s">
+        <v>25</v>
+      </c>
+      <c r="K5" t="s">
         <v>26</v>
-      </c>
-      <c r="K5" t="s">
-        <v>27</v>
       </c>
       <c r="L5">
         <v>135</v>
@@ -837,51 +837,51 @@
         <v>135</v>
       </c>
       <c r="N5" t="s">
+        <v>27</v>
+      </c>
+      <c r="O5" t="s">
         <v>28</v>
       </c>
-      <c r="O5" t="s">
+      <c r="Q5" t="s">
         <v>29</v>
       </c>
-      <c r="Q5" t="s">
+      <c r="R5" t="s">
         <v>30</v>
       </c>
-      <c r="R5" t="s">
-        <v>31</v>
-      </c>
       <c r="S5" t="s">
-        <v>32</v>
+        <v>59</v>
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
+        <v>48</v>
+      </c>
+      <c r="B6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" t="s">
+        <v>49</v>
+      </c>
+      <c r="D6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F6" t="s">
+        <v>50</v>
+      </c>
+      <c r="G6" t="s">
         <v>51</v>
       </c>
-      <c r="B6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" t="s">
-        <v>52</v>
-      </c>
-      <c r="D6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E6" t="s">
-        <v>23</v>
-      </c>
-      <c r="F6" t="s">
-        <v>53</v>
-      </c>
-      <c r="G6" t="s">
-        <v>54</v>
-      </c>
       <c r="I6" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="J6" t="s">
+        <v>25</v>
+      </c>
+      <c r="K6" t="s">
         <v>26</v>
-      </c>
-      <c r="K6" t="s">
-        <v>27</v>
       </c>
       <c r="L6">
         <v>8888</v>
@@ -890,54 +890,54 @@
         <v>8888</v>
       </c>
       <c r="N6" t="s">
+        <v>27</v>
+      </c>
+      <c r="O6" t="s">
         <v>28</v>
       </c>
-      <c r="O6" t="s">
+      <c r="Q6" t="s">
         <v>29</v>
       </c>
-      <c r="Q6" t="s">
+      <c r="R6" t="s">
         <v>30</v>
       </c>
-      <c r="R6" t="s">
-        <v>31</v>
-      </c>
       <c r="S6" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B7" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C7" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D7" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F7" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G7" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="H7" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="I7" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="J7" t="s">
+        <v>25</v>
+      </c>
+      <c r="K7" t="s">
         <v>26</v>
-      </c>
-      <c r="K7" t="s">
-        <v>27</v>
       </c>
       <c r="L7">
         <v>445</v>
@@ -946,42 +946,42 @@
         <v>445</v>
       </c>
       <c r="N7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P7" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="B8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C8" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E8" t="s">
         <v>22</v>
       </c>
-      <c r="E8" t="s">
-        <v>23</v>
-      </c>
       <c r="F8" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="G8" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="I8" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="J8" t="s">
+        <v>25</v>
+      </c>
+      <c r="K8" t="s">
         <v>26</v>
-      </c>
-      <c r="K8" t="s">
-        <v>27</v>
       </c>
       <c r="L8">
         <v>8888</v>
@@ -990,51 +990,51 @@
         <v>8888</v>
       </c>
       <c r="N8" t="s">
+        <v>27</v>
+      </c>
+      <c r="O8" t="s">
         <v>28</v>
       </c>
-      <c r="O8" t="s">
-        <v>29</v>
-      </c>
       <c r="Q8" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="R8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="S8" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" t="s">
         <v>19</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>20</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
         <v>21</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>22</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>23</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>24</v>
       </c>
-      <c r="G9" t="s">
+      <c r="I9" t="s">
+        <v>24</v>
+      </c>
+      <c r="J9" t="s">
         <v>25</v>
       </c>
-      <c r="I9" t="s">
-        <v>25</v>
-      </c>
-      <c r="J9" t="s">
+      <c r="K9" t="s">
         <v>26</v>
-      </c>
-      <c r="K9" t="s">
-        <v>27</v>
       </c>
       <c r="L9">
         <v>2101</v>
@@ -1043,19 +1043,16 @@
         <v>2101</v>
       </c>
       <c r="N9" t="s">
+        <v>27</v>
+      </c>
+      <c r="O9" t="s">
         <v>28</v>
       </c>
-      <c r="O9" t="s">
+      <c r="Q9" t="s">
         <v>29</v>
       </c>
-      <c r="Q9" t="s">
+      <c r="R9" t="s">
         <v>30</v>
-      </c>
-      <c r="R9" t="s">
-        <v>31</v>
-      </c>
-      <c r="S9" t="s">
-        <v>32</v>
       </c>
     </row>
   </sheetData>
